--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -724,16 +724,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -810,16 +828,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-18.4</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,16 +914,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-18.9</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -895,16 +949,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>0.758</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1046,16 +1118,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>225.337</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -647,24 +647,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Sep-26</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>National Bank of Ukraine</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>18-Sep-26</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NBU</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18-Sep-26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>raised 50 bps</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -704,19 +700,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ukrstat</t>
+          <t>State Statistics Service of Ukraine (Ukrstat)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>core 8.1%</t>
-        </is>
-      </c>
+          <t>10-Sep-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -786,22 +778,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance / IMF</t>
+          <t>Ministry of Finance of Ukraine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt; 2026 projected 105-122.6%</t>
+          <t>State and state-guaranteed debt</t>
         </is>
       </c>
     </row>
@@ -999,7 +991,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>National Bank of Ukraine</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1009,7 +1001,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross international reserves; $48.7B end-Aug-26</t>
+          <t>NBU gross international reserves (preliminary)</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1043,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>National Bank of Ukraine</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1301,7 +1293,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EFF (4-year)</t>
+          <t>Extended Fund Facility (EFF), 4-year</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1417,7 +1409,11 @@
         <v>98.40000000000001</v>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ministry of Finance of Ukraine, 31-Dec-25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>National Bank of Ukraine</t>
+          <t>NBU key rate decision (+50 bps)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>State Statistics Service of Ukraine (Ukrstat)</t>
+          <t>Ukrstat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -739,11 +739,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -778,7 +774,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>end-2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>State and state-guaranteed debt</t>
+          <t>state debt</t>
         </is>
       </c>
     </row>
@@ -843,11 +839,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -929,11 +921,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -991,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>National Bank of Ukraine</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1001,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NBU gross international reserves (preliminary)</t>
+          <t>NBU gross international reserves</t>
         </is>
       </c>
     </row>
@@ -1011,16 +999,34 @@
           <t>net_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>38.6</v>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IMF reserve template</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>net of predetermined and contingent one-year drains</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1043,7 +1049,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>National Bank of Ukraine</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1111,7 +1117,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>225.337</v>
+        <v>225.3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1133,11 +1139,7 @@
           <t>08-Oct-26</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1293,11 +1295,8 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extended Fund Facility (EFF), 4-year</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>15.6</v>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1346,8 +1345,14 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" s="2" t="n">
+        <v>225.3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1356,8 +1361,14 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1376,8 +1387,14 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="C5" s="2" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1386,8 +1403,14 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" s="2" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IMF WEO, 08-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1411,7 +1434,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ministry of Finance of Ukraine, 31-Dec-25</t>
+          <t>Ministry of Finance of Ukraine (state debt), 31-Dec-25</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NBU key rate decision (+50 bps)</t>
+          <t>NBU</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>end-2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt</t>
+          <t>state debt, end-2025</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>net of predetermined and contingent one-year drains</t>
+          <t>gross reserves net of predetermined and contingent one-year drains</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+          <t>4-year EFF</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ministry of Finance of Ukraine (state debt), 31-Dec-25</t>
+          <t>Ministry of Finance of Ukraine (state debt), 08-Oct-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt, end-2025</t>
+          <t>state debt</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>gross reserves net of predetermined and contingent one-year drains</t>
+          <t>net of predetermined and contingent one-year drains</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-year EFF</t>
+          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>18-Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -784,12 +784,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt</t>
+          <t>state debt, end-year</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>31-Aug-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>net of predetermined and contingent one-year drains</t>
+          <t>gross reserves net of predetermined and contingent one-year drains (IMF reserve template)</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ministry of Finance of Ukraine (state debt), 08-Oct-26</t>
+          <t>Ministry of Finance of Ukraine, end-2025</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt, end-year</t>
+          <t>state debt</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31-Aug-26</t>
+          <t>08-Oct-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26, SDR 503M, about $690M disbursed)</t>
+          <t>4-year EFF</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ministry of Finance of Ukraine, end-2025</t>
+          <t>Ministry of Finance of Ukraine (state debt), end-2025</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt</t>
+          <t>State debt, end-2025</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>gross reserves net of predetermined and contingent one-year drains (IMF reserve template)</t>
+          <t>gross reserves net of predetermined and contingent one-year drains</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-year EFF</t>
+          <t>4-year EFF (first review completed 20-Jul-26; SDR 503M, about $690M disbursed)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 09-Oct-26</t>
+          <t>as of 19-Oct-26</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>NBU rate decision</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ukrstat</t>
+          <t>Ukrstat / NBU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -779,17 +779,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ministry of Finance of Ukraine</t>
+          <t>MinFin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>State debt, end-2025</t>
+          <t>state debt</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>NBU reserves release</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NBU gross international reserves</t>
+          <t>gross official reserve assets (NBU); gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IMF reserve template</t>
+          <t>IMF International Reserves and FX Liquidity template</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>gross reserves net of predetermined and contingent one-year drains</t>
+          <t>gross reserves net of predetermined and contingent one-year drains (IMF reserve template)</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NBU</t>
+          <t>NBU reserves release</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1281,9 +1281,9 @@
           <t>Ca</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jan-26</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4-year EFF (first review completed 20-Jul-26; SDR 503M, about $690M disbursed)</t>
+          <t>4-year EFF</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Combined 2nd and 3rd reviews targeted Dec-26; staff mission expected Nov-26</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1363,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IMF WEO, 08-Oct-26</t>
+          <t>IMF WEO, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1379,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IMF WEO, 08-Oct-26</t>
+          <t>IMF WEO, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1405,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IMF WEO, 08-Oct-26</t>
+          <t>IMF WEO, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1421,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IMF WEO, 08-Oct-26</t>
+          <t>IMF WEO, 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1447,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ministry of Finance of Ukraine (state debt), end-2025</t>
+          <t>MinFin (state debt), end-2025</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Ukraine_Sovereign_Model.xlsx
+++ b/models/sovereigns/Ukraine_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 19-Oct-26</t>
+          <t>as of 28-Oct-26</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
+          <t>built 28-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/ukraine.json</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NBU rate decision</t>
+          <t>NBU, rate decision 18-Sep-26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -695,17 +695,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ukrstat / NBU</t>
+          <t>Ukrstat via ukranews and Forbes.ua; IMF CPI database (9.998%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -779,17 +779,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MinFin</t>
+          <t>Ministry of Finance of Ukraine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>31-Dec-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>state debt</t>
+          <t>state debt, end-year</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross official reserve assets (NBU); gold treatment not stated</t>
+          <t>gross, NBU headline reserves (gold inclusion not stated)</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>38.6</v>
+        <v>36.955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Aug-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IMF International Reserves and FX Liquidity template</t>
+          <t>IMF International Reserves template</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01-Oct-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1281,11 +1281,6 @@
           <t>Ca</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1308,7 +1303,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Combined 2nd and 3rd reviews targeted Dec-26; staff mission expected Nov-26</t>
+          <t>Combined 2nd and 3rd reviews targeted Dec-26; mission Nov-26</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1358,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IMF WEO, 09-Oct-26</t>
+          <t>IMF WEO, 19-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1374,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IMF WEO, 09-Oct-26</t>
+          <t>IMF WEO, 19-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1400,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IMF WEO, 09-Oct-26</t>
+          <t>IMF WEO, 19-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1416,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>IMF WEO, 09-Oct-26</t>
+          <t>IMF WEO, 19-Oct-26</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1442,7 @@
       <c r="C8" s="2" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MinFin (state debt), end-2025</t>
+          <t>Ministry of Finance of Ukraine, 31-Dec-25</t>
         </is>
       </c>
     </row>
